--- a/results/06-2026/beta/inputs-comparison-06-2026.xlsx
+++ b/results/06-2026/beta/inputs-comparison-06-2026.xlsx
@@ -3962,7 +3962,7 @@
         <v>1949.7</v>
       </c>
       <c r="N22" t="n">
-        <v>371.652997</v>
+        <v>402.652997</v>
       </c>
       <c r="O22" t="n">
         <v>79.2681428571429</v>
@@ -4120,7 +4120,7 @@
         <v>1956.4</v>
       </c>
       <c r="N23" t="n">
-        <v>347.8256195</v>
+        <v>378.8256195</v>
       </c>
       <c r="O23" t="n">
         <v>75.1961428571429</v>
@@ -4278,7 +4278,7 @@
         <v>1989.7</v>
       </c>
       <c r="N24" t="n">
-        <v>373.806928</v>
+        <v>310.806928</v>
       </c>
       <c r="O24" t="n">
         <v>75.1961428571429</v>
@@ -4436,7 +4436,7 @@
         <v>1971.8</v>
       </c>
       <c r="N25" t="n">
-        <v>354.1033188</v>
+        <v>291.1033188</v>
       </c>
       <c r="O25" t="n">
         <v>75.1961428571429</v>
@@ -4594,7 +4594,7 @@
         <v>1986.8</v>
       </c>
       <c r="N26" t="n">
-        <v>309.279</v>
+        <v>299.279</v>
       </c>
       <c r="O26" t="n">
         <v>75.1961428571429</v>
@@ -4752,7 +4752,7 @@
         <v>1993.22590350582</v>
       </c>
       <c r="N27" t="n">
-        <v>289.298764494522</v>
+        <v>299.298764494522</v>
       </c>
       <c r="O27" t="n">
         <v>75.1961428571429</v>
@@ -4910,7 +4910,7 @@
         <v>1995.8134991428</v>
       </c>
       <c r="N28" t="n">
-        <v>293.149342835201</v>
+        <v>303.149342835201</v>
       </c>
       <c r="O28" t="n">
         <v>75.1961428571429</v>
@@ -5068,7 +5068,7 @@
         <v>2008.16227191654</v>
       </c>
       <c r="N29" t="n">
-        <v>295.028009083171</v>
+        <v>305.028009083171</v>
       </c>
       <c r="O29" t="n">
         <v>75.1961428571429</v>
@@ -5226,7 +5226,7 @@
         <v>2019.41841567176</v>
       </c>
       <c r="N30" t="n">
-        <v>297.93504</v>
+        <v>307.93504</v>
       </c>
       <c r="O30" t="n">
         <v>75.1961428571429</v>
@@ -5384,7 +5384,7 @@
         <v>2029.86829015562</v>
       </c>
       <c r="N31" t="n">
-        <v>300.870715074303</v>
+        <v>310.870715074303</v>
       </c>
       <c r="O31" t="n">
         <v>75.1961428571429</v>
@@ -5542,7 +5542,7 @@
         <v>2040.8916978889</v>
       </c>
       <c r="N32" t="n">
-        <v>303.835316548609</v>
+        <v>313.835316548609</v>
       </c>
       <c r="O32" t="n">
         <v>75.1961428571429</v>
@@ -5700,7 +5700,7 @@
         <v>2046.64306409843</v>
       </c>
       <c r="N33" t="n">
-        <v>306.829129446497</v>
+        <v>316.829129446497</v>
       </c>
       <c r="O33" t="n">
         <v>75.1961428571429</v>
@@ -5858,7 +5858,7 @@
         <v>2050.39853806318</v>
       </c>
       <c r="N34" t="n">
-        <v>309.8524416</v>
+        <v>319.8524416</v>
       </c>
       <c r="O34" t="n">
         <v>75.1961428571429</v>
@@ -14686,7 +14686,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-31</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -14842,7 +14842,7 @@
         <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-31</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -14998,7 +14998,7 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -15154,7 +15154,7 @@
         <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -15310,7 +15310,7 @@
         <v>-0.299999999999955</v>
       </c>
       <c r="N26" t="n">
-        <v>10.3</v>
+        <v>0.300000000000011</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -15466,7 +15466,7 @@
         <v>-0.299007333929922</v>
       </c>
       <c r="N27" t="n">
-        <v>-9.69704397803599</v>
+        <v>0.302956021964008</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -15622,7 +15622,7 @@
         <v>-0.301345656650028</v>
       </c>
       <c r="N28" t="n">
-        <v>-9.694058829185</v>
+        <v>0.305941170815004</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -15778,7 +15778,7 @@
         <v>-0.303210184089949</v>
       </c>
       <c r="N29" t="n">
-        <v>-9.69104426644799</v>
+        <v>0.308955733552011</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -15934,7 +15934,7 @@
         <v>-0.304909736699983</v>
       </c>
       <c r="N30" t="n">
-        <v>-9.68799999999999</v>
+        <v>0.312000000000012</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -16090,7 +16090,7 @@
         <v>-0.306487551610189</v>
       </c>
       <c r="N31" t="n">
-        <v>-9.68492573715702</v>
+        <v>0.315074262842984</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -16246,7 +16246,7 @@
         <v>-0.308151963650062</v>
       </c>
       <c r="N32" t="n">
-        <v>-9.681821182352</v>
+        <v>0.318178817648004</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -16402,7 +16402,7 @@
         <v>-0.309020356030032</v>
       </c>
       <c r="N33" t="n">
-        <v>-9.67868603710701</v>
+        <v>0.321313962892987</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -16558,7 +16558,7 @@
         <v>-0.309587390860088</v>
       </c>
       <c r="N34" t="n">
-        <v>-9.67552000000001</v>
+        <v>0.324479999999994</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>

--- a/results/06-2026/beta/inputs-comparison-06-2026.xlsx
+++ b/results/06-2026/beta/inputs-comparison-06-2026.xlsx
@@ -4761,7 +4761,7 @@
         <v>3462.63828806306</v>
       </c>
       <c r="Q27" t="n">
-        <v>5016.82407316799</v>
+        <v>5034.82407316799</v>
       </c>
       <c r="R27" t="n">
         <v>2636.67277279961</v>
@@ -4818,7 +4818,7 @@
         <v>345.800981275389</v>
       </c>
       <c r="AJ27" t="n">
-        <v>-2948.33688878016</v>
+        <v>-2950.49688878016</v>
       </c>
       <c r="AK27" t="n">
         <v>-1520.57073273595</v>
@@ -4919,7 +4919,7 @@
         <v>3496.13488552031</v>
       </c>
       <c r="Q28" t="n">
-        <v>5054.29727260192</v>
+        <v>5072.3688445901</v>
       </c>
       <c r="R28" t="n">
         <v>2666.55786673422</v>
@@ -4976,7 +4976,7 @@
         <v>351.399497154</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-2979.11656149239</v>
+        <v>-2983.44515013097</v>
       </c>
       <c r="AK28" t="n">
         <v>-1540.85167674406</v>
@@ -5077,7 +5077,7 @@
         <v>3526.99675561438</v>
       </c>
       <c r="Q29" t="n">
-        <v>5087.75196760069</v>
+        <v>5105.89539616312</v>
       </c>
       <c r="R29" t="n">
         <v>2694.62842095072</v>
@@ -5134,7 +5134,7 @@
         <v>354.271506931401</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-3013.21935321439</v>
+        <v>-3018.64515328046</v>
       </c>
       <c r="AK29" t="n">
         <v>-1559.81072089017</v>
@@ -5292,7 +5292,7 @@
         <v>355.632237528028</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-3068.49028318578</v>
+        <v>-3072.83178893256</v>
       </c>
       <c r="AK30" t="n">
         <v>-1578.64108314823</v>
@@ -5450,7 +5450,7 @@
         <v>356.997746402807</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-3113.06700025285</v>
+        <v>-3116.31990028589</v>
       </c>
       <c r="AK31" t="n">
         <v>-1597.04323859381</v>
@@ -5608,7 +5608,7 @@
         <v>358.575658685331</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-3137.71870416414</v>
+        <v>-3140.97160419717</v>
       </c>
       <c r="AK32" t="n">
         <v>-1615.12920029267</v>
@@ -5766,7 +5766,7 @@
         <v>365.20640021081</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-3160.25881752647</v>
+        <v>-3163.51171755951</v>
       </c>
       <c r="AK33" t="n">
         <v>-1632.22206089396</v>
@@ -5924,7 +5924,7 @@
         <v>373.030059953625</v>
       </c>
       <c r="AJ34" t="n">
-        <v>-3194.97444411764</v>
+        <v>-3198.22734415068</v>
       </c>
       <c r="AK34" t="n">
         <v>-1649.45008021301</v>
@@ -15475,7 +15475,7 @@
         <v>0.605726981209955</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.00461304586952</v>
+        <v>19.0046130458695</v>
       </c>
       <c r="R27" t="n">
         <v>3.24169175989982</v>
@@ -15532,7 +15532,7 @@
         <v>3.56193743472198</v>
       </c>
       <c r="AJ27" t="n">
-        <v>-0.240553565509799</v>
+        <v>-2.40055356551011</v>
       </c>
       <c r="AK27" t="n">
         <v>-0.317003011180077</v>
@@ -15631,7 +15631,7 @@
         <v>0.611586615149918</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.00924026932989</v>
+        <v>19.0808122575099</v>
       </c>
       <c r="R28" t="n">
         <v>3.27830657205004</v>
@@ -15688,7 +15688,7 @@
         <v>4.48371455702204</v>
       </c>
       <c r="AJ28" t="n">
-        <v>-0.301662397829659</v>
+        <v>-4.63025103640985</v>
       </c>
       <c r="AK28" t="n">
         <v>-0.746399799839992</v>
@@ -15787,7 +15787,7 @@
         <v>0.616985350410232</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.01486194820973</v>
+        <v>19.1582905106397</v>
       </c>
       <c r="R29" t="n">
         <v>3.31296318914974</v>
@@ -15844,7 +15844,7 @@
         <v>5.14734324795501</v>
       </c>
       <c r="AJ29" t="n">
-        <v>-0.363169048850068</v>
+        <v>-5.78896911491984</v>
       </c>
       <c r="AK29" t="n">
         <v>-0.94945387693997</v>
@@ -16000,7 +16000,7 @@
         <v>5.96218456313198</v>
       </c>
       <c r="AJ30" t="n">
-        <v>-0.430380954820066</v>
+        <v>-4.77188670160012</v>
       </c>
       <c r="AK30" t="n">
         <v>-1.15425523038016</v>
@@ -16156,7 +16156,7 @@
         <v>5.00106004776001</v>
       </c>
       <c r="AJ31" t="n">
-        <v>-0.497960471479928</v>
+        <v>-3.75086050452001</v>
       </c>
       <c r="AK31" t="n">
         <v>-1.36057067796992</v>
@@ -16312,7 +16312,7 @@
         <v>5.26797199254298</v>
       </c>
       <c r="AJ32" t="n">
-        <v>-0.563258205530019</v>
+        <v>-3.81615823856009</v>
       </c>
       <c r="AK32" t="n">
         <v>-1.56876883207997</v>
@@ -16468,7 +16468,7 @@
         <v>5.11238900368801</v>
       </c>
       <c r="AJ33" t="n">
-        <v>-0.628978207750151</v>
+        <v>-3.88187824079023</v>
       </c>
       <c r="AK33" t="n">
         <v>-1.7788733236298</v>
@@ -16624,7 +16624,7 @@
         <v>4.831157834419</v>
       </c>
       <c r="AJ34" t="n">
-        <v>-0.636862696479966</v>
+        <v>-3.88976272952004</v>
       </c>
       <c r="AK34" t="n">
         <v>-2.0269376588501</v>
